--- a/data/pipelines/pipeline_capacity_sources.xlsx
+++ b/data/pipelines/pipeline_capacity_sources.xlsx
@@ -537,14 +537,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Source type: Official (EIA), Company SEC filing (10-K), Company website, Derived, Industry reference, or Press. Press figures could not be confirmed from an operator or official document, so those lines are drawn thin. The one Industry reference (Colonial north of Greensboro, NC) is drawn, because EIA publishes no figure for that stretch and a thin line would show Colonial ending in North Carolina.</t>
+          <t>Source type: Official (EIA), Company SEC filing (10-K), Company website, Derived, Industry reference, or Press. Press and industry-reference figures could not be confirmed from an operator or official document; they are the best figures available and are drawn at the reported value.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Width on map: 'No (thin)' lines appear on the map at a fixed thin width.</t>
+          <t>Width on map: 'No (thin)' lines have no capacity figure from any source and appear at a fixed thin width.</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Plantation Pipe Line</t>
+          <t>Products SE Pipeline (formerly Plantation)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Now called the Products (SE) Pipeline. Earlier: about 710,000 b/d after a 2001 expansion (Kinder Morgan Energy Partners 10-K405 for 2001: https://www.sec.gov/Archives/edgar/data/888228/000095012902000816/h94309e10-k405.txt). Drawn on the mainline only; laterals are thin</t>
+          <t>Renamed from Plantation: Kinder Morgan's 10-K for 2025 lists the "Products (SE) pipeline" (3,181 miles, 51% owned via Products (SE) Pipe Line Corporation): https://www.sec.gov/Archives/edgar/data/1506307/000150630726000011/kmi-20251231.htm. Earlier: about 710,000 b/d after a 2001 expansion (Kinder Morgan Energy Partners 10-K405 for 2001: https://www.sec.gov/Archives/edgar/data/888228/000095012902000816/h94309e10-k405.txt). Drawn on the mainline only; laterals are thin</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -1482,12 +1482,12 @@
       <c r="J14" s="6" t="inlineStr"/>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed from an operator or official document; drawn thin</t>
+          <t>Not confirmed from an operator or official document; drawn at the reported figure</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>No (thin)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
@@ -1537,12 +1537,12 @@
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Not confirmed from an operator or official document; drawn thin</t>
+          <t>Not confirmed from an operator or official document; drawn at the reported figure</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>No (thin)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
@@ -1592,12 +1592,12 @@
       <c r="J16" s="6" t="inlineStr"/>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed from an operator or official document; drawn thin</t>
+          <t>Not confirmed from an operator or official document; drawn at the reported figure</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>No (thin)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
@@ -1651,12 +1651,12 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Current operating status not confirmed; drawn thin</t>
+          <t>Current operating status not confirmed; drawn at its 2002 design capacity</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>No (thin)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
@@ -3490,12 +3490,12 @@
       <c r="J48" s="6" t="inlineStr"/>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Not confirmed from an operator or official document; drawn thin</t>
+          <t>Not confirmed from an operator or official document; drawn at the reported figure</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>No (thin)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M48" s="6" t="n">

--- a/data/pipelines/pipeline_capacity_sources.xlsx
+++ b/data/pipelines/pipeline_capacity_sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Pipelines" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipelines'!$A$1:$M$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipelines'!$A$1:$M$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -530,14 +530,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Measure: 'Capacity' unless stated. Two lines show throughput (actual volume) because the operator publishes no capacity; one is derived from two published figures, and the arithmetic is in its notes.</t>
+          <t>Measure: 'Capacity' unless stated. Where no capacity is published, a line is drawn at its throughput (actual volume, with the year); one figure is derived from two published figures, with the arithmetic in its notes.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Source type: Official (EIA), Company SEC filing (10-K), Company website, Derived, Industry reference, or Press. Press and industry-reference figures could not be confirmed from an operator or official document; they are the best figures available and are drawn at the reported value.</t>
+          <t>Source type: Official (EIA) or Official (EIA study), Company SEC filing (10-K), Company website, Derived, or Press. EIA studies are its regional Transportation Fuels Markets reports (West Coast 2015, East and Gulf Coasts 2016, Midwest and Rocky Mountains 2017), which list capacity by pipeline segment. Press figures could not be confirmed from an operator or official document; they are the best available and are drawn at the reported value.</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <f>COUNTA(Pipelines!B2:B48)</f>
+        <f>COUNTA(Pipelines!B2:B96)</f>
         <v/>
       </c>
     </row>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNTIF(Pipelines!L2:L48,"Yes")</f>
+        <f>COUNTIF(Pipelines!L2:L96,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>SUMIFS(Pipelines!D2:D48,Pipelines!A2:A48,"Refined products",Pipelines!L2:L48,"Yes")</f>
+        <f>SUMIFS(Pipelines!D2:D96,Pipelines!A2:A96,"Refined products",Pipelines!L2:L96,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>SUMIFS(Pipelines!D2:D48,Pipelines!A2:A48,"Crude oil",Pipelines!L2:L48,"Yes")</f>
+        <f>SUMIFS(Pipelines!D2:D96,Pipelines!A2:A96,"Crude oil",Pipelines!L2:L96,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -795,33 +795,41 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>1585000</v>
+        <v>1389000</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Capacity (Line 3 885k + Line 4 700k)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>Capacity (Line 3 885,000 + Line 4 504,000)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Industry reference (not directly verified)</t>
+          <t>Official (EIA study)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>McKinsey Energy Insights, Refinery Reference Desk: Colonial pipeline</t>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 5</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>https://www.mckinseyenergyinsights.com/resources/refinery-reference-desk/colonial-pipeline/</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Northern Lines Line 3 Mixed Products Greensboro, NC Linden, NJ 885,000 Line 4 Mixed Products Greensboro, NC Dorsey, MD 504,000 Total 1,389,000</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>The page could not be opened to confirm; figures as indexed by search: Line 3 885,000 b/d Greensboro to Linden, Line 4 700,000 b/d Greensboro to Baltimore. EIA gives no official figure north of Greensboro. Drawn at their sum so the line is not shown ending in North Carolina</t>
+          <t>Line 3 runs to Linden, NJ (New York Harbor) and Line 4 to Dorsey/Sykesville, MD (Baltimore). The same report gives the southern lines as Line 1 1,370,000 (gasoline) and Line 2 1,160,000 (distillate), total 2,530,000</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1502,12 +1510,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Laurel Pipeline</t>
+          <t>Laurel Pipeline, Duncansville to Coraopolis (Pittsburgh)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia, PA to Pittsburgh, PA</t>
+          <t>Duncansville, PA to Coraopolis, PA</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
@@ -1515,38 +1523,42 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Capacity (press-reported)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr"/>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Official (EIA study)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Philadelphia Inquirer / Global Energy Monitor</t>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
-          <t>https://www.gem.wiki/Laurel_Pipeline</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Not confirmed from an operator or official document; drawn at the reported figure</t>
-        </is>
-      </c>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Duncansville, PA Coraopolis, PA 180,000</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1557,51 +1569,55 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>CALNEV Pipeline</t>
+          <t>Laurel Pipeline, Mechanicsburg to Duncansville</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Colton, CA to Las Vegas, NV</t>
+          <t>Mechanicsburg, PA to Duncansville, PA</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>128000</v>
+        <v>216000</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Volume (press-reported)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Official (EIA study)</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Wikipedia / Global Energy Monitor</t>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>https://www.gem.wiki/Calnev_Oil_Products_Pipeline</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr"/>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>Not confirmed from an operator or official document; drawn at the reported figure</t>
-        </is>
-      </c>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA Duncansville, PA 216,000</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1612,46 +1628,50 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Centennial Pipeline</t>
+          <t>Laurel Pipeline, Booth (Philadelphia) to Mechanicsburg</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Beaumont, TX to Bourbon, IL</t>
+          <t>Booth, PA to Mechanicsburg, PA</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>210000</v>
+        <v>312000</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Design capacity at opening (2002)</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Official (EIA study)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Power Engineering (2002)</t>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>https://www.power-eng.com/operations-maintenance/centennial-pipeline-announces-beginning-of-full-operation/</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Laurel Pipeline Booth, PA Mechanicsburg, PA 312,000</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Current operating status not confirmed; drawn at its 2002 design capacity</t>
+          <t>The EIA route for this stretch is labelled Buckeye</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1671,49 +1691,59 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>SFPP (Kinder Morgan Pacific system)</t>
+          <t>CALNEV Pipeline</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Los Angeles and Bay Area to Arizona, Nevada and Oregon; El Paso to Phoenix</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="n"/>
+          <t>Colton, CA to Las Vegas, NV</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>108300</v>
+      </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
+          <t>Throughput (2012 average)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Kinder Morgan Products Pipelines</t>
+          <t>Kinder Morgan, Inc., Form 10-K for 2012</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>https://kindermorgan.com/Operations/Products/Index</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
+          <t>https://www.sec.gov/Archives/edgar/data/1506307/000150630713000015/kmi-20121231x10k.htm</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>In 2012, the Calnev pipeline system transported approximately 108,300 barrels per day of refined products</t>
+        </is>
+      </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>Kinder Morgan publishes no line capacity for SFPP. The Western Gateway line (Texas to Arizona, 230,000 b/d design) reached a final investment decision in Aug 2026</t>
+          <t>Capacity not published. Wikipedia and Global Energy Monitor give about 128,000 b/d</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>No (thin)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1724,67 +1754,79 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Networks with no single capacity (Magellan/ONEOK, NuStar, Buckeye, TEPPCO, Marathon, BP, Sunoco and others)</t>
+          <t>Centennial Pipeline</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Gulf Coast and Mid-Continent to the Midwest and Northeast</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="n"/>
+          <t>Beaumont, TX to Bourbon, IL</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>210000</v>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Not published</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA study)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>e.g. Magellan Midstream Partners, Form 10-K for 2022: a 9,800-mile refined products system with no capacity by line</t>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 33</t>
         </is>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1126975/000112697523000064/mmp-20221231.htm</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Centennial Pipeline Beaumont, TX Bourbon, IL 795 210,000 (A) Largely idle since mid-2011.</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Drawn thin</t>
+          <t>EIA: largely idle since mid-2011; its owners (Marathon, Enterprise) have considered converting it to carry NGLs south. Drawn at capacity</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>No (thin)</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Refined products</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Enbridge Canadian Mainline</t>
+          <t>SFPP East Line (Kinder Morgan)</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Edmonton, AB to the US border at Neche, ND / Gretna, MB</t>
+          <t>El Paso, TX to Phoenix, AZ</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>3200000</v>
+        <v>200000</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -1793,30 +1835,34 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA study)</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>Enbridge Inc., Form 10-K for 2025</t>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Tables 30 and 41</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>The Canadian Mainline includes six adjacent pipelines with a combined operating capacity of approximately 3.2 mmbpd that connect with the Lakehead System at the Canada/US border</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="inlineStr"/>
+          <t>Kinder Morgan SFPP East Line El Paso, TX Phoenix, AZ 230 200,000</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>Two parallel pipelines (EIA West Coast report, 2015)</t>
+        </is>
+      </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1829,51 +1875,55 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Refined products</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Enbridge Lakehead System, border to Superior (excluding Line 67)</t>
+          <t>SFPP West Line (Kinder Morgan)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Neche, ND to Superior, WI</t>
+          <t>Colton (Los Angeles area), CA to Phoenix, AZ</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>2400000</v>
+        <v>69000</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Derived capacity</t>
+          <t>Throughput (2013)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Derived from official and company figures</t>
+          <t>Official (EIA study)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Enbridge 10-K for 2025 (Mainline 3.2 mmbpd) less Line 67 (800,000 b/d, EIA liquids pipeline projects database)</t>
+          <t>EIA, West Coast Transportation Fuels Markets, Sep 2015</t>
         </is>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr"/>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd5/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>The Kinder Morgan West Line ... in 2013, it moved 35,000 b/d of gasoline, 6,000 b/d of jet, and 28,000 b/d of distillate to Phoenix, Arizona.</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Line 67 (Alberta Clipper) is drawn separately, so this segment is drawn at 3.2M less 0.8M. Enbridge does not publish a figure for this segment on its own</t>
+          <t>Capacity not published; EIA notes the West Line operates well below capacity. Drawn at 2013 throughput (35,000 + 6,000 + 28,000)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1888,32 +1938,26 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Refined products</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Enbridge Line 5</t>
+          <t>SFPP North Line, Oregon Line and San Diego Line (Kinder Morgan)</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Superior, WI to Sarnia, ON via Michigan</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>540000</v>
-      </c>
+          <t>Los Angeles and Bay Area to Arizona, Nevada and Oregon; El Paso to Phoenix</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n"/>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Company website</t>
@@ -1921,87 +1965,79 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>Enbridge: What is Line 5?</t>
+          <t>Kinder Morgan Products Pipelines</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>https://www.enbridge.com/projects-and-infrastructure/public-awareness/line-5-answering-your-questions/what-is-line-5</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>transports up to 540,000 barrels per day (bpd) of light crude oil, light synthetic crude, and natural gas liquids</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr"/>
+          <t>https://kindermorgan.com/Operations/Products/Index</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>No capacity published for these lines. Kinder Morgan: its Pacific system as a whole moves more than one million b/d (Pacific Operations brochure, March 2025: https://www.kindermorgan.com/WWWKM/media/Documents/2025-March-Pacific-ops-brochure.pdf)</t>
+        </is>
+      </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No (thin)</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Crude oil</t>
+          <t>Refined products</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Enbridge Alberta Clipper (Line 67)</t>
+          <t>Networks with no single capacity (Magellan/ONEOK, NuStar, Buckeye, TEPPCO, Marathon, BP, Sunoco and others)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Hardisty, AB to Superior, WI</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>800000</v>
-      </c>
+          <t>Gulf Coast and Mid-Continent to the Midwest and Northeast</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (IDs 83 and 128)</t>
+          <t>e.g. Magellan Midstream Partners, Form 10-K for 2022: a 9,800-mile refined products system with no capacity by line</t>
         </is>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Upgrading of pumps brought U.S. capacity up from 570,000 b/d to 800,000 b/d</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr"/>
+          <t>https://www.sec.gov/Archives/edgar/data/1126975/000112697523000064/mmp-20221231.htm</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Drawn thin where no segment figure exists. Segment figures from the EIA regional studies are listed as their own rows</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>1</v>
-      </c>
+          <t>No (thin)</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -2011,16 +2047,16 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Enbridge Southern Access (Line 61)</t>
+          <t>Enbridge Canadian Mainline</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Superior, WI to Flanagan, IL</t>
+          <t>Edmonton, AB to the US border at Neche, ND / Gretna, MB</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1200000</v>
+        <v>3200000</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
@@ -2029,27 +2065,27 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 199)</t>
+          <t>Enbridge Inc., Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>Capacity increased from 950,000 b/d to 1,200,000 b/d.</t>
+          <t>The Canadian Mainline includes six adjacent pipelines with a combined operating capacity of approximately 3.2 mmbpd that connect with the Lakehead System at the Canada/US border</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr"/>
@@ -2070,20 +2106,20 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Spearhead Pipeline</t>
+          <t>Enbridge Lakehead System, border to Superior (excluding Line 67)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Flanagan, IL to Cushing, OK</t>
+          <t>Neche, ND to Superior, WI</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>193000</v>
+        <v>2400000</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Derived capacity</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2093,25 +2129,25 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Derived from official and company figures</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Enbridge Inc., Form 10-K for 2025</t>
+          <t>Enbridge 10-K for 2025 (Mainline 3.2 mmbpd) less Line 67 (800,000 b/d, EIA liquids pipeline projects database)</t>
         </is>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>The Spearhead Pipeline has a capacity of approximately 193 kbpd.</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Line 67 (Alberta Clipper) is drawn separately, so this segment is drawn at 3.2M less 0.8M. Enbridge does not publish a figure for this segment on its own</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2129,16 +2165,16 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Ozark Pipeline (Midcontinent)</t>
+          <t>Enbridge Line 5</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Cushing, OK to Wood River, IL</t>
+          <t>Superior, WI to Sarnia, ON via Michigan</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>360000</v>
+        <v>540000</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
@@ -2147,27 +2183,27 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 138)</t>
+          <t>Enbridge: What is Line 5?</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+          <t>https://www.enbridge.com/projects-and-infrastructure/public-awareness/line-5-answering-your-questions/what-is-line-5</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>Capacity expanded from about 230,000 b/d to 360,000 b/d.</t>
+          <t>transports up to 540,000 barrels per day (bpd) of light crude oil, light synthetic crude, and natural gas liquids</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr"/>
@@ -2188,16 +2224,16 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Express Pipeline</t>
+          <t>Enbridge Alberta Clipper (Line 67)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Hardisty, AB to Casper, WY</t>
+          <t>Hardisty, AB to Superior, WI</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>310000</v>
+        <v>800000</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -2206,27 +2242,27 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Enbridge Inc., Form 10-K for 2025</t>
+          <t>EIA, Liquids pipeline projects database (IDs 83 and 128)</t>
         </is>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>The 310 kbpd Express Pipeline carries crude oil to US refining markets in the Rocky Mountains area</t>
+          <t>Upgrading of pumps brought U.S. capacity up from 570,000 b/d to 800,000 b/d</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
@@ -2247,16 +2283,16 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Platte Pipeline</t>
+          <t>Enbridge Southern Access (Line 61)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Casper, WY to Wood River, IL</t>
+          <t>Superior, WI to Flanagan, IL</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>145000</v>
+        <v>1200000</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
@@ -2265,34 +2301,30 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA)</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Enbridge Inc., Form 10-K for 2025</t>
+          <t>EIA, Liquids pipeline projects database (ID 199)</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>The 145 to 164 kbpd Platte Pipeline</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>164k b/d on the first segment (Casper to Guernsey); 145k b/d beyond</t>
-        </is>
-      </c>
+          <t>Capacity increased from 950,000 b/d to 1,200,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr"/>
       <c r="L28" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2310,16 +2342,16 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Keystone Pipeline, Hardisty to Steele City</t>
+          <t>Spearhead Pipeline</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Hardisty, AB to Steele City, NE</t>
+          <t>Flanagan, IL to Cushing, OK</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>591000</v>
+        <v>193000</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2328,41 +2360,37 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 3)</t>
+          <t>Enbridge Inc., Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>brought capacity of the entire system up to 591,000 b/d</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Now owned by South Bow. Later optimisations are reported to have raised it to about 622,000 b/d (S&amp;P Global, July 2022). Legs beyond Steele City to Patoka and Cushing are drawn thin: their split is not published</t>
-        </is>
-      </c>
+          <t>The Spearhead Pipeline has a capacity of approximately 193 kbpd.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2373,16 +2401,16 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Keystone Gulf Coast Project</t>
+          <t>Ozark Pipeline (Midcontinent)</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Cushing, OK to Port Arthur, TX</t>
+          <t>Cushing, OK to Wood River, IL</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>700000</v>
+        <v>360000</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
@@ -2391,7 +2419,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2401,7 +2429,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 45)</t>
+          <t>EIA, Liquids pipeline projects database (ID 138)</t>
         </is>
       </c>
       <c r="I30" s="8" t="inlineStr">
@@ -2411,7 +2439,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Extension of Keystone Pipeline that goes from Cushing, Oklahoma, to refineries in Port Arthur, Texas. Expandable to 830,000 b/d.</t>
+          <t>Capacity expanded from about 230,000 b/d to 360,000 b/d.</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr"/>
@@ -2432,16 +2460,16 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Dakota Access Pipeline</t>
+          <t>Express Pipeline</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Bakken, ND to Patoka, IL</t>
+          <t>Hardisty, AB to Casper, WY</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>750000</v>
+        <v>310000</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2460,7 +2488,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Enbridge Inc., Form 10-K for 2025 (Bakken Pipeline System)</t>
+          <t>Enbridge Inc., Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I31" s="10" t="inlineStr">
@@ -2470,7 +2498,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>The Bakken Pipeline System consists of the Dakota Access Pipeline ... and the Energy Transfer Crude Oil Pipeline ... Current capacity is approximately 750 kbpd of crude oil</t>
+          <t>The 310 kbpd Express Pipeline carries crude oil to US refining markets in the Rocky Mountains area</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
@@ -2491,16 +2519,16 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Energy Transfer Crude Oil Pipeline (ETCO)</t>
+          <t>Platte Pipeline</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Patoka, IL to Nederland, TX</t>
+          <t>Casper, WY to Wood River, IL</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>750000</v>
+        <v>145000</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
@@ -2519,7 +2547,7 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Enbridge Inc., Form 10-K for 2025 (Bakken Pipeline System)</t>
+          <t>Enbridge Inc., Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -2529,12 +2557,12 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Current capacity is approximately 750 kbpd of crude oil</t>
+          <t>The 145 to 164 kbpd Platte Pipeline</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Same system capacity as Dakota Access</t>
+          <t>164k b/d on the first segment (Casper to Guernsey); 145k b/d beyond</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -2554,16 +2582,16 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Pony Express Pipeline</t>
+          <t>Keystone Pipeline, Hardisty to Steele City</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Guernsey, WY to Cushing, OK</t>
+          <t>Hardisty, AB to Steele City, NE</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>400000</v>
+        <v>591000</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2572,7 +2600,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2582,7 +2610,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 145)</t>
+          <t>EIA, Liquids pipeline projects database (ID 3)</t>
         </is>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -2592,10 +2620,14 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Pump enhancements expand capacity from 320,000 b/d to 400,000 b/d</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
+          <t>brought capacity of the entire system up to 591,000 b/d</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Now owned by South Bow. Later optimisations are reported to have raised it to about 622,000 b/d (S&amp;P Global, July 2022). Legs beyond Steele City to Patoka and Cushing are drawn thin: their split is not published</t>
+        </is>
+      </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2613,16 +2645,16 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Saddlehorn Pipeline</t>
+          <t>Keystone Gulf Coast Project</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Platteville, CO to Cushing, OK</t>
+          <t>Cushing, OK to Port Arthur, TX</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>290000</v>
+        <v>700000</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
@@ -2631,34 +2663,30 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA)</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Plains All American, Form 10-K for 2025</t>
+          <t>EIA, Liquids pipeline projects database (ID 45)</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1070423/000107042326000014/paa-20251231.htm</t>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>owns approximately 290,000 barrels per day of capacity in the Saddlehorn Pipeline</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>The EIA route combines Saddlehorn and Grand Mesa; drawn at Saddlehorn's capacity</t>
-        </is>
-      </c>
+          <t>Extension of Keystone Pipeline that goes from Cushing, Oklahoma, to refineries in Port Arthur, Texas. Expandable to 830,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr"/>
       <c r="L34" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2676,16 +2704,16 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Seaway Pipeline</t>
+          <t>Dakota Access Pipeline</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Cushing, OK to Freeport/Houston, TX</t>
+          <t>Bakken, ND to Patoka, IL</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>950000</v>
+        <v>750000</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2704,17 +2732,17 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners, Form 10-K for 2025</t>
+          <t>Enbridge Inc., Form 10-K for 2025 (Bakken Pipeline System)</t>
         </is>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1061219/000106121926000006/epd-20251231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>The aggregate transportation capacity of the Longhaul System is approximately 950 MBPD</t>
+          <t>The Bakken Pipeline System consists of the Dakota Access Pipeline ... and the Energy Transfer Crude Oil Pipeline ... Current capacity is approximately 750 kbpd of crude oil</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
@@ -2735,16 +2763,16 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Gray Oak Pipeline</t>
+          <t>Energy Transfer Crude Oil Pipeline (ETCO)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Permian Basin to Corpus Christi and Freeport</t>
+          <t>Patoka, IL to Nederland, TX</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>900000</v>
+        <v>750000</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
@@ -2763,27 +2791,31 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+          <t>Enbridge Inc., Form 10-K for 2025 (Bakken Pipeline System)</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/895728/000119312526049810/enb-20251231.htm</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Gray Oak Pipeline Texas 7 862 900</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr"/>
+          <t>Current capacity is approximately 750 kbpd of crude oil</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Same system capacity as Dakota Access</t>
+        </is>
+      </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="M36" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2794,16 +2826,16 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Cactus Pipeline</t>
+          <t>Pony Express Pipeline</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>McCamey, TX to Gardendale/Corpus Christi, TX</t>
+          <t>Guernsey, WY to Cushing, OK</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>390000</v>
+        <v>400000</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -2812,34 +2844,30 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Plains All American, Form 10-K for 2025</t>
+          <t>EIA, Liquids pipeline projects database (ID 145)</t>
         </is>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1070423/000107042326000014/paa-20251231.htm</t>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>the Cactus Pipeline, which has a capacity of 390,000 barrels per day</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Cactus II (Wink to Ingleside, 670,000 b/d per EIA) is not a separate route in the EIA layer</t>
-        </is>
-      </c>
+          <t>Pump enhancements expand capacity from 320,000 b/d to 400,000 b/d</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2857,16 +2885,16 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>EPIC Crude Pipeline</t>
+          <t>Saddlehorn Pipeline</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Permian Basin to Corpus Christi</t>
+          <t>Platteville, CO to Cushing, OK</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>600000</v>
+        <v>290000</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
@@ -2875,30 +2903,34 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 163)</t>
+          <t>Plains All American, Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1070423/000107042326000014/paa-20251231.htm</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Database field Added Capacity: 600,000 b/d (EPIC Crude Pipeline, completed 2020)</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr"/>
+          <t>owns approximately 290,000 barrels per day of capacity in the Saddlehorn Pipeline</t>
+        </is>
+      </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>The EIA route combines Saddlehorn and Grand Mesa; drawn at Saddlehorn's capacity</t>
+        </is>
+      </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2916,16 +2948,16 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BridgeTex Pipeline</t>
+          <t>Seaway Pipeline</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Colorado City, TX to Houston, TX</t>
+          <t>Cushing, OK to Freeport/Houston, TX</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>440000</v>
+        <v>950000</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -2944,17 +2976,17 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Plains All American, Form 10-K for 2025</t>
+          <t>Enterprise Products Partners, Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1070423/000107042326000014/paa-20251231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1061219/000106121926000006/epd-20251231.htm</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>The BridgeTex pipeline has a capacity of approximately 440,000 barrels per day</t>
+          <t>The aggregate transportation capacity of the Longhaul System is approximately 950 MBPD</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
@@ -2975,16 +3007,16 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Longhorn Pipeline</t>
+          <t>Gray Oak Pipeline</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Crane, TX to Houston, TX</t>
+          <t>Permian Basin to Corpus Christi and Freeport</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>275000</v>
+        <v>900000</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
@@ -2993,27 +3025,27 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 69)</t>
+          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
         </is>
       </c>
       <c r="I40" s="8" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Capacity increased from 225,000 b/d to 275,000 b/d.</t>
+          <t>Gray Oak Pipeline Texas 7 862 900</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr"/>
@@ -3023,7 +3055,7 @@
         </is>
       </c>
       <c r="M40" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -3034,50 +3066,50 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Basin Pipeline</t>
+          <t>Cactus Pipeline</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Wink/Midland, TX to Cushing, OK</t>
+          <t>McCamey, TX to Gardendale/Corpus Christi, TX</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>600000</v>
+        <v>390000</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Capacity (Wink to Midland segment)</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 90)</t>
+          <t>Plains All American, Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1070423/000107042326000014/paa-20251231.htm</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>bring total capacity from 240,000 b/d to 600,000 b/d</t>
+          <t>the Cactus Pipeline, which has a capacity of 390,000 barrels per day</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>This figure is for the Wink to Midland segment; the segment north to Cushing is smaller</t>
+          <t>Cactus II (Wink to Ingleside, 670,000 b/d per EIA) is not a separate route in the EIA layer</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -3097,16 +3129,16 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Midland-to-ECHO 1 (Midland to Sealy)</t>
+          <t>EPIC Crude Pipeline</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Midland, TX to Sealy/Houston, TX</t>
+          <t>Permian Basin to Corpus Christi</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>620000</v>
+        <v>600000</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
@@ -3115,27 +3147,27 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA)</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Enterprise Products Partners, Form 10-K for 2025</t>
+          <t>EIA, Liquids pipeline projects database (ID 163)</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1061219/000106121926000006/epd-20251231.htm</t>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>The Midland-to-ECHO 1 Pipeline has an approximate maximum transportation capacity of up to 620 MBPD</t>
+          <t>Database field Added Capacity: 600,000 b/d (EPIC Crude Pipeline, completed 2020)</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr"/>
@@ -3156,16 +3188,16 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Diamond Pipeline</t>
+          <t>BridgeTex Pipeline</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Cushing, OK to Memphis, TN</t>
+          <t>Colorado City, TX to Houston, TX</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>200000</v>
+        <v>440000</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3194,7 +3226,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>The Diamond Pipeline has a total capacity of approximately 200,000 barrels per day.</t>
+          <t>The BridgeTex pipeline has a capacity of approximately 440,000 barrels per day</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
@@ -3215,16 +3247,16 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Bayou Bridge Pipeline</t>
+          <t>Longhorn Pipeline</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Nederland, TX to St. James, LA</t>
+          <t>Crane, TX to Houston, TX</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>480000</v>
+        <v>275000</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
@@ -3233,27 +3265,27 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Company SEC filing</t>
+          <t>Official (EIA)</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+          <t>EIA, Liquids pipeline projects database (ID 69)</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Bayou Bridge Texas/Louisiana 40 213 480</t>
+          <t>Capacity increased from 225,000 b/d to 275,000 b/d.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr"/>
@@ -3263,7 +3295,7 @@
         </is>
       </c>
       <c r="M44" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3274,25 +3306,25 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Capline</t>
+          <t>Basin Pipeline</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Patoka, IL to St. James, LA (flow reversed southbound in 2021)</t>
+          <t>Wink/Midland, TX to Cushing, OK</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>300000</v>
+        <v>600000</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Initial capacity after reversal</t>
+          <t>Capacity (Wink to Midland segment)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3302,7 +3334,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 188)</t>
+          <t>EIA, Liquids pipeline projects database (ID 90)</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -3312,12 +3344,12 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Reversal of 1,300,000 b/d pipeline so that it flows south. Initial capacity in 2021 Q4 is 300,000 b/d.</t>
+          <t>bring total capacity from 240,000 b/d to 600,000 b/d</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Operated by Marathon since the reversal</t>
+          <t>This figure is for the Wink to Midland segment; the segment north to Cushing is smaller</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3326,7 +3358,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3337,16 +3369,16 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Double H Pipeline</t>
+          <t>Midland-to-ECHO 1 (Midland to Sealy)</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Baker, MT / Bakken to Guernsey, WY</t>
+          <t>Midland, TX to Sealy/Houston, TX</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>84000</v>
+        <v>620000</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
@@ -3355,27 +3387,27 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>Official (EIA)</t>
+          <t>Company SEC filing</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 72)</t>
+          <t>Enterprise Products Partners, Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I46" s="8" t="inlineStr">
         <is>
-          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1061219/000106121926000006/epd-20251231.htm</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Database field Added Capacity: 84,000 b/d (Double H Pipeline, completed 2015)</t>
+          <t>The Midland-to-ECHO 1 Pipeline has an approximate maximum transportation capacity of up to 620 MBPD</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr"/>
@@ -3385,7 +3417,7 @@
         </is>
       </c>
       <c r="M46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3396,16 +3428,16 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Glacier Pipeline</t>
+          <t>Diamond Pipeline</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Cut Bank, MT to Billings, MT</t>
+          <t>Cushing, OK to Memphis, TN</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>124000</v>
+        <v>200000</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -3424,17 +3456,17 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+          <t>Plains All American, Form 10-K for 2025</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1070423/000107042326000014/paa-20251231.htm</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Glacier Montana 79 800 124</t>
+          <t>The Diamond Pipeline has a total capacity of approximately 200,000 barrels per day.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
@@ -3455,55 +3487,2951 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>Bayou Bridge Pipeline</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Nederland, TX to St. James, LA</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>480000</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>Company SEC filing</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Bayou Bridge Texas/Louisiana 40 213 480</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Capline</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Patoka, IL to St. James, LA (flow reversed southbound in 2021)</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Initial capacity after reversal</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 188)</t>
+        </is>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Reversal of 1,300,000 b/d pipeline so that it flows south. Initial capacity in 2021 Q4 is 300,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Operated by Marathon since the reversal</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Double H Pipeline</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Baker, MT / Bakken to Guernsey, WY</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>84000</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 72)</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Database field Added Capacity: 84,000 b/d (Double H Pipeline, completed 2015)</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr"/>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Glacier Pipeline</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Cut Bank, MT to Billings, MT</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>124000</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Company SEC filing</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Glacier Montana 79 800 124</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>Mid-Valley Pipeline</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Longview, TX to Samaria, MI</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n">
+      <c r="D52" s="7" t="n">
         <v>240000</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Capacity (press-reported)</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr"/>
-      <c r="G48" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr">
         <is>
           <t>Press</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H52" s="6" t="inlineStr">
         <is>
           <t>Global Energy Monitor</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>https://www.gem.wiki/Mid-Valley_Oil_Pipeline</t>
         </is>
       </c>
-      <c r="J48" s="6" t="inlineStr"/>
-      <c r="K48" s="6" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr">
         <is>
           <t>Not confirmed from an operator or official document; drawn at the reported figure</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="n">
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="n">
         <v>3</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Colonial Line 17 (Atlanta to Bainbridge)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA to Bainbridge, GA</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 19</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Line 17 Atlanta, GA Bainbridge, GA 150,000</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>Central Florida Pipeline (16-inch)</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Tampa, FL to Orlando, FL</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>115000</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 23</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Kinder Morgan Central Florida Pipeline Tampa, FL (16 - inch) Orlando, FL 110 115,000</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>The parallel 10-inch line (jet fuel) has no separate figure</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Parkway Pipeline</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Norco, LA to Collins, MS</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 33</t>
+        </is>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Parkway Pipeline Norco, LA Collins, MS 141 110,000</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>Collins Pipeline</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Meraux, LA to Collins, MS</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>130000</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 33</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Collins Pipeline Meraux, LA Collins, MS 125 130,000</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr"/>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Bengal Pipeline</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Garyville and Norco, LA to Baton Rouge, LA</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>305000</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 33</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Bengal Pipeline Garyville and Norco, LA Baton Rouge, LA 158 305,000</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Second Bengal route (Convent to Baton Rouge, 210,000 b/d) drawn thin</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>TEPPCO Mainline (Enterprise TE Products)</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Beaumont, TX to Seymour, IN</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>330000</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>Capacity (EIA estimate)</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 20</t>
+        </is>
+      </c>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>TEPPCO Mainline (P-2) Beaumont, TX Seymour, IN 921 20 330,000 a [a Estimated]</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>EIA notes TEPPCO no longer ships distillates or jet fuel into the Midwest on this line</t>
+        </is>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Buckeye, Eagle Point to Macungie</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Eagle Point, NJ to Macungie, PA</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>204000</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Eastern System Eagle Point, PA Macungie and Sinking Spring, PA 204,000</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>Buckeye, Sinking Spring to Linden and Long Island</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Sinking Spring, PA via Macungie and Linden, NJ to New York</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>302000</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Capacity (Linden to Macungie segment)</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Linden, NJ Macungie, PA 302,000</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>EIA draws this as one route; the figure is its Linden to Macungie segment. Long Island lines: 120,000 (airports) and 138,500 (Brooklyn, Inwood)</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Buckeye, Mantua to Coraopolis</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Mantua, OH to Coraopolis, PA</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>55200</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Midwest System Mantua, OH Coraopolis, PA 55,200</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>Buckeye, New Haven to Springfield</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>New Haven, CT to Springfield, MA</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>62000</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 12</t>
+        </is>
+      </c>
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Buckeye Partners New Haven, CT Springfield, MA 100 62,000</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr"/>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Buckeye, Portland to Bangor</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Portland, ME to Bangor, ME</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>19200</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 12</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Portland, ME Bangor, ME 124 19,200</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Buckeye Lower V system</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Dubuque, IA to Kansas City, MO</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>41000</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>Throughput (2015)</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 35</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Buckeye Pipe Line Transportation (Lower V system) Dubuque, IA Kansas City, MO 650 12 41,000</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>2015 shipments of transportation fuels</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Sunoco Harbor Pipeline</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Woodbury, NJ to Linden, NJ</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Harbor Woodbury, NJ Linden, NJ 180,000</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Sunoco, Twin Oaks to Newark</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Twin Oaks, PA to Newark, NJ</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>125000</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>Twin Oaks, PA Newark, NJ 125,000</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr"/>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Sunoco, Philadelphia to Rochester and Buffalo</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Reading, PA to Rochester and Buffalo, NY</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>64800</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA Rochester and Buffalo, NY 64,800</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Sunoco, Montello to Kingston</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Reading/Montello, PA to Kingston, PA</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Montello, PA Kingston, PA 11,000</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr"/>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Sunoco Allegheny Access</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Toledo and Lima, OH to Delmont (Pittsburgh), PA</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>85000</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 17</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Allegheny Access Toledo and Lima, OH Delmont, PA 85,000</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Marathon, Robinson to Louisville</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Robinson, IL to Louisville, KY</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>92000</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Robinson Products Robinson, IL Louisville, KY 129 16 92,000</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>Louisville to Lexington: 36,000</t>
+        </is>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Marathon, Robinson to Lima</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Robinson, IL to Lima, OH</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>51000</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Robinson, IL Lima, OH 250 10 51,000</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>The parallel EIA route on this corridor is drawn thin</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Marathon Wabash, Robinson to Champaign</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Robinson, IL to Champaign, IL</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>99000</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Wabash Robinson, IL Champaign, IL 86 12 99,000</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr"/>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Marathon Wabash, Wood River to Champaign and Chicago</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Wood River, IL to Champaign, IL and Griffith/Hammond, IN</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>71000</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Capacity (Wood River to Champaign)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Wood River, IL Champaign, IL 130 12 71,000</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>EIA draws this as one route; Champaign to Griffith/Hammond is 85,000</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Marathon, Wood River to Clermont</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Wood River, IL to Clermont (Indianapolis), IN</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>48000</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>Wood River, IL Clermont, IN 317 10 48,000</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr"/>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Marathon, Robinson to Mt. Vernon</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Robinson, IL to Mt. Vernon, IN</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>43000</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Robinson, IL Mt. Vernon, IN 79 10 43,000</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Marathon, Kenova to Columbus</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Kenova, WV to Columbus, OH</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>68000</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Ohio River Pipe Line (ORPL) Products Kenova, WV Columbus, OH 150 14 68,000</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr"/>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Marathon, East Sparta to Heath</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>East Sparta, OH to Heath, OH</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>29000</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I77" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>East Sparta, OH Heath, OH 81 8 29,000</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Marathon, Heath to Dayton</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Heath, OH to Dayton, OH</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>24000</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>Heath, OH Dayton, OH 108 6 24,000</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M78" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Marathon, Heath to Findlay</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Heath, OH to Findlay, OH</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 10</t>
+        </is>
+      </c>
+      <c r="I79" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Heath, OH Findlay, OH 100 10/8 18,000</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Magellan Chase Pipeline</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>El Dorado, KS to Aurora (Denver), CO</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 42</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>Capacity on the segment from El Dorado to Aurora is 60,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Magellan, Houston to Odessa</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Houston, TX to Odessa, TX</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>110000</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 30</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Houston, TX Odessa, TX Not avail. 110,000</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Magellan, Odessa to El Paso</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Odessa, TX to El Paso, TX</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>64000</v>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 30</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Odessa, TX El Paso, TX Not avail. 64,000</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>The parallel EIA route on this corridor is drawn thin</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>El Paso to Albuquerque line</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>El Paso, TX to Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>28200</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Tables 30 and 41</t>
+        </is>
+      </c>
+      <c r="I83" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>El Paso, TX Albuquerque, NM 257 28,200</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>EIA lists this line under Magellan; the EIA route layer labels it Plains</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>NuStar McKee to Denver</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>McKee refinery (Sunray, TX) to Denver, CO</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>32500</v>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 43</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>McKee-Denver McKee refinery (Sunray, TX) Denver, CO 357 10 32,500</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr"/>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>NuStar Amarillo to Albuquerque</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Amarillo, TX to Albuquerque, NM</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>17200</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 41</t>
+        </is>
+      </c>
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>NuStar Central West Pipeline Amarillo, TX Albuquerque, NM 293 17,200</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>NuStar North Pipeline</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Mandan, ND to Roseville (Twin Cities), MN</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>47000</v>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>Throughput (2015, from Mandan)</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 25</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>North Pipeline Mainline Mandan, ND Roseville, MN 440 10/8 47,000</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>2015 shipments originating at the Mandan refinery</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>NuStar Valley Pipeline</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Corpus Christi, TX to Rio Grande Valley</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 214)</t>
+        </is>
+      </c>
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Increased Valley Pipeline by 45,000 to 90,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Holly, Big Spring to Wichita Falls</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Big Spring, TX to Wichita Falls, TX and Duncan, OK</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 30</t>
+        </is>
+      </c>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Big Spring, TX Wichita Falls, TX 227 23,000</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>Wichita Falls to Duncan: 21,000</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Sinclair Medicine Bow Pipeline</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Sinclair, WY to Denver, CO</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>27600</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 44</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Sinclair, WY Denver, CO 204 6/10 27,600</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Sinclair, Casper to Sinclair</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Casper, WY to Sinclair, WY</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>21600</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 44</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>Sinclair Transportation Casper, WY Sinclair, WY N/A 8/12 21,600</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>Bidirectional</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Sinclair, Olathe to Carrollton and Iowa</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Olathe, KS to Carrollton, MO and Montrose, IA</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>15600</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Throughput (Dec 2013)</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 37</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Sinclair Transportation Olathe, KS Carrollton, MO N/A 8 15,600 c [c Average volumes transported as of December 2013]</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Cenex Pipeline (CHS)</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Laurel, MT to Fargo, ND</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>46000</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Throughput (2015)</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 44</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>Cenex Pipeline Laurel, MT Fargo, ND 683 8/10 N/A 46,000</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>Capacity not published; 2015 shipments</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>CHS McPherson to Council Bluffs</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>McPherson, KS to Council Bluffs, IA</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>43000</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Throughput (2015)</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 37</t>
+        </is>
+      </c>
+      <c r="I93" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>CHS Council Bluffs Pipeline McPherson, KS Council Bluffs, IA 227 N/A 43,000 b [b Average volumes transported in 2015]</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Koch Wisconsin Pipeline</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Rosemount (Twin Cities), MN to Waupun and Milwaukee, WI</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Throughput (EIA estimate, 2015)</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 27</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>Koch Pipeline Co. Rosemount, MN Waupun, WI 261 12/10 80,000 d [d Estimated as one-third of prime supplier sales volumes of gasoline and distillates in Wisconsin]</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr"/>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M94" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>West Shore Pipe Line</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Chicago area to Milwaukee and Green Bay, WI</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>326000</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Throughput (2015, West Shore and Badger combined)</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 12</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>West Shore Romeo, IL Busse Station, IL 36 16 326,000</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Shipments for the West Shore and Badger systems together; the segment north of Milwaukee was shut in 2016 for rebuilding</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>BP, Wood River to Milan</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Wood River, IL to Milan, MO</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>Throughput (2015)</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 35</t>
+        </is>
+      </c>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>Wood River, IL Milan, MO N/A N/A 17,000</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr"/>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M48"/>
+  <autoFilter ref="A1:M96"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
@@ -3552,6 +6480,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/pipelines/pipeline_capacity_sources.xlsx
+++ b/data/pipelines/pipeline_capacity_sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Pipelines" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipelines'!$A$1:$M$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pipelines'!$A$1:$M$112</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B13" s="4">
-        <f>COUNTA(Pipelines!B2:B96)</f>
+        <f>COUNTA(Pipelines!B2:B112)</f>
         <v/>
       </c>
     </row>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNTIF(Pipelines!L2:L96,"Yes")</f>
+        <f>COUNTIF(Pipelines!L2:L112,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>SUMIFS(Pipelines!D2:D96,Pipelines!A2:A96,"Refined products",Pipelines!L2:L96,"Yes")</f>
+        <f>SUMIFS(Pipelines!D2:D112,Pipelines!A2:A112,"Refined products",Pipelines!L2:L112,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>SUMIFS(Pipelines!D2:D96,Pipelines!A2:A96,"Crude oil",Pipelines!L2:L96,"Yes")</f>
+        <f>SUMIFS(Pipelines!D2:D112,Pipelines!A2:A112,"Crude oil",Pipelines!L2:L112,"Yes")</f>
         <v/>
       </c>
     </row>
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3315,16 +3315,16 @@
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>600000</v>
+        <v>450000</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Capacity (Wink to Midland segment)</t>
+          <t>Capacity (Colorado City to Cushing segment)</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>EIA, Liquids pipeline projects database (ID 90)</t>
+          <t>EIA, Liquids pipeline projects database (IDs 19 and 90)</t>
         </is>
       </c>
       <c r="I45" s="10" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>bring total capacity from 240,000 b/d to 600,000 b/d</t>
+          <t>Segment from Colorado City, Texas, to Cushing, Oklahoma, had its capacity increased from 400,000 b/d to 450,000 b/d.</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>This figure is for the Wink to Midland segment; the segment north to Cushing is smaller</t>
+          <t>EIA draws Basin as one route from the Permian to Cushing; the Wink to Midland segment was expanded to 600,000 b/d in 2015 (ID 90)</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -6430,8 +6430,988 @@
         <v>1</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Colonial Lines 19 and 20 (Atlanta to Nashville)</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Atlanta, GA via Chattanooga to Nashville, TN</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Throughput (2015, EIA range 250,000 to 300,000)</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>EIA, PADDs 2 and 4 Transportation Fuels Markets, Jan 2017, Table 18</t>
+        </is>
+      </c>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd2n4/pdf/transportation_fuels.pdf</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Colonial Pipeline Line 19 Atlanta, GA Chattanooga Jct./Nashville, TN 10/12 250,000 - 300,000</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Drawn at the low end of EIA's range</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Seminoe Pipeline</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Billings, MT to Casper and Sinclair, WY</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Company SEC filing</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+        </is>
+      </c>
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>Seminoe Montana/Wyoming 100 342 50</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>The EIA route layer spells it "Seminole"</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>NuStar, McKee to Southlake (Dallas–Fort Worth)</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>McKee refinery (Sunray, TX) to Southlake, TX</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>26000</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 30</t>
+        </is>
+      </c>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>McKee, TX Southlake, TX 375 26,000</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>NuStar, McKee to El Paso</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>McKee refinery (Sunray, TX) to El Paso, TX</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 30</t>
+        </is>
+      </c>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>McKee, TX El Paso, TX 408 42,000</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr"/>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Refined products</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>NuStar, Three Rivers to San Antonio</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Three Rivers, TX to San Antonio, TX</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>33500</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA study)</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>EIA, East Coast and Gulf Coast Transportation Fuels Markets (prepared by ICF), Feb 2016, Table 26</t>
+        </is>
+      </c>
+      <c r="I101" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/analysis/transportationfuels/padd1n3/pdf/transportation_fuels_padd1n3.pdf</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Three Rivers, TX San Antonio, TX 85 33,500</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Keystone Pipeline, Steele City to Patoka</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Steele City, NE to Patoka, IL</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>435000</v>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 2)</t>
+        </is>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>Goes from Hardisty in Alberta, Canada, down through Steele City, Nebraska, and to Patoka, Illinois. [Added capacity 435,000 b/d]</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr"/>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Keystone Pipeline, Steele City to Cushing</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Steele City, NE to Cushing, OK</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>156000</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 3)</t>
+        </is>
+      </c>
+      <c r="I103" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Extended existing pipeline from Steele City, Nebraska, to Cushing, Oklahoma, and brought capacity of the entire system up to 591,000 b/d. [Added capacity 156,000 b/d]</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Zydeco Pipeline (Houston to Houma)</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Houston, TX via Port Neches, TX to Houma, LA</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>375000</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>Capacity (Port Neches to Houma segment)</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (IDs 36 and 114)</t>
+        </is>
+      </c>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>Increased capacity of Port Neches, Texas, to Houma, Louisiana, segment from 360,000 b/d to 375,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>Houston to Port Neches segment: 250,000 b/d (ID 36)</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Permian Express 2</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Colorado City, TX to Corsicana, TX</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 84)</t>
+        </is>
+      </c>
+      <c r="I105" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Garden City, Texas, to Colorado City, Texas, segment has 20-inch diameter pipeline, Colorado City to Corsicana, Texas, has 24-inch diameter pipeline. [Added capacity 230,000 b/d]</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Marathon, Patoka to Catlettsburg</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Patoka, IL via Owensboro, KY to Catlettsburg, KY</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>270000</v>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 22)</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>Capacity increased from 256,000 b/d to 270,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr"/>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Marathon, Patoka to Lima and Canton</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Patoka, IL to Lima and Canton, OH</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>267000</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Capacity (Patoka to Lima)</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Official (EIA)</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>EIA, Liquids pipeline projects database (ID 111)</t>
+        </is>
+      </c>
+      <c r="I107" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eia.gov/petroleum/xls/EIA_LiqPipProject.xlsx</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Capacity increased from 249,000 b/d to 267,000 b/d.</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>EIA route continues past Lima to Canton</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Red River Pipeline</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Cushing, OK to Longview, TX</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>235000</v>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>Company SEC filing</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>Plains All American, Form 10-K for 2025</t>
+        </is>
+      </c>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1070423/000107042326000014/paa-20251231.htm</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>The Red River Pipeline is an approximately 235,000 barrel per day capacity pipeline that extends from our Cushing Terminal in Oklahoma to Longview, Texas</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>EIA route layer label: "CK Red River"</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M108" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Phillips 66 Oklahoma Crude system</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Wichita Falls, TX to Ponca City, OK</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Company SEC filing</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+        </is>
+      </c>
+      <c r="I109" s="10" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Oklahoma Crude Texas/Oklahoma 100 217 100</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Matched to the EIA route by operator and endpoints</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Phillips 66 West Texas Crude system</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Odessa, TX to Borger, TX</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>Company SEC filing</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>West Texas Crude Texas 100 1,079 140</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>Matched to the EIA route by operator and endpoints</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Phillips 66 California Line 200</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>San Joaquin Valley to Rodeo (San Francisco Bay), CA</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Company SEC filing</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Phillips 66, Form 10-K for 2025, pipeline table</t>
+        </is>
+      </c>
+      <c r="I111" s="10" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1534701/000153470126000006/psx-20251231.htm</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Line 200 California 100 228 100</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Matched to the EIA route by operator and endpoints</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Crude oil</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Trans Mountain Pipeline</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Edmonton, AB to Burnaby (Vancouver), BC</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>890000</v>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>Official (Canada Energy Regulator)</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>Canada Energy Regulator, Market Snapshot (2025): Trans Mountain Expansion eases pipeline constraints</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2025/market-snapshot-trans-mountain-expansion-eases-pipeline-constraints-and-increases-exports-to-overseas-markets.html</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>The Trans Mountain Expansion Project came online in May 2024, nearly tripling the capacity of the Trans Mountain System to a total of 890 thousand barrels per day.</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>Now owned by Trans Mountain Corporation (Canadian government); the EIA layer still lists Kinder Morgan. Also listed in EIA's product layer, where it is left off to avoid drawing it twice</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M96"/>
+  <autoFilter ref="A1:M112"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
@@ -6528,6 +7508,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId111"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
